--- a/balance_tables/武器.xlsx
+++ b/balance_tables/武器.xlsx
@@ -1232,13 +1232,13 @@
         <v>1</v>
       </c>
       <c r="S2" s="55" t="n">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="T2" s="55" t="n">
         <v>1</v>
       </c>
       <c r="U2" s="55" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3">
@@ -1309,13 +1309,13 @@
         <v>1</v>
       </c>
       <c r="S3" s="55" t="n">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="T3" s="55" t="n">
         <v>1</v>
       </c>
       <c r="U3" s="55" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="4">
@@ -1392,7 +1392,7 @@
         <v>0.5</v>
       </c>
       <c r="U4" s="55" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>

--- a/balance_tables/武器.xlsx
+++ b/balance_tables/武器.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gameproduct\小厨西\balance_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB79703-6A18-4AE2-B7E9-B81B746DFC60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{692FFF80-B9E2-403B-959F-C446977161EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -772,7 +772,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-26DA-4345-896C-5CA314BBF0BF}"/>
+              <c16:uniqueId val="{00000000-6B56-4358-92F0-30B7D509D454}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -976,7 +976,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-947F-4C83-ABB6-E3D3B20E0C5B}"/>
+              <c16:uniqueId val="{00000000-584F-4628-9465-3471472057DB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1654,11 +1654,11 @@
       </c>
       <c r="C10">
         <f>武器!G5</f>
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="D10">
         <f>B10/C10</f>
-        <v>1.5</v>
+        <v>1.6666666666666665</v>
       </c>
       <c r="E10">
         <f>IF(武器!C5="carrot_sweep",武器!W5,IF(武器!C5="orbiting_mushroom",武器!M5*POWER(1.5,INT(ABS(武器!N5)*武器!J5/(4*PI())))*IF(MOD(ABS(武器!N5)*武器!J5/(2*PI()),2)&lt;=1,1,1+0.5*(MOD(ABS(武器!N5)*武器!J5/(2*PI()),2)-1)),武器!H5*武器!J5))</f>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="J10">
         <f>D10</f>
-        <v>1.5</v>
+        <v>1.6666666666666665</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -2145,7 +2145,7 @@
         <v>3</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H5">
         <v>680</v>
@@ -2222,13 +2222,13 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>680</v>
+        <v>2878.36</v>
       </c>
       <c r="I6">
         <v>17</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="K6">
         <v>999</v>

--- a/balance_tables/武器.xlsx
+++ b/balance_tables/武器.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gameproduct\小厨西\balance_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{692FFF80-B9E2-403B-959F-C446977161EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE6B1B5-40BA-4956-8479-815C880C0025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -772,7 +772,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6B56-4358-92F0-30B7D509D454}"/>
+              <c16:uniqueId val="{00000000-F84F-4EC1-B928-E28E72B2756A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -976,7 +976,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-584F-4628-9465-3471472057DB}"/>
+              <c16:uniqueId val="{00000000-749A-4DA6-8E8C-DD43FE1148D7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2222,13 +2222,13 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>2878.36</v>
+        <v>680</v>
       </c>
       <c r="I6">
         <v>17</v>
       </c>
       <c r="J6">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="K6">
         <v>999</v>
@@ -2240,7 +2240,7 @@
         <v>120</v>
       </c>
       <c r="N6">
-        <v>3.2</v>
+        <v>12.56636</v>
       </c>
       <c r="O6">
         <v>1.2</v>
